--- a/products/japanese-closet/excel/products.xlsx
+++ b/products/japanese-closet/excel/products.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="1" r:id="R1acd7ee8e7c44e2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="2" r:id="Rf36637c5dbd14a6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="1" r:id="R10859ceeedf84bfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="2" r:id="R5dfe7327a22042d9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1133,8 +1133,8 @@
       <x:c r="N8" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O8" t="s">
-        <x:v>80</x:v>
+      <x:c r="O8" t="str">
+        <x:v>images/products/JP-CORNER-BRACKET.png</x:v>
       </x:c>
       <x:c r="T8" t="s">
         <x:v>70</x:v>
@@ -1507,6 +1507,9 @@
       </x:c>
       <x:c r="N17" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="O17" t="str">
+        <x:v>images/products/JP-JEWELRY-BOX.png</x:v>
       </x:c>
       <x:c r="P17" t="s">
         <x:v>134</x:v>

--- a/products/japanese-closet/excel/products.xlsx
+++ b/products/japanese-closet/excel/products.xlsx
@@ -376,7 +376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z24"/>
+  <dimension ref="A1:Z26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.80000019073486"/>
   <cols>
     <col width="26.109375" customWidth="1" style="2" min="1" max="1"/>
@@ -583,7 +583,12 @@
       <c r="N2" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t>images/products/JP-POST.png</t>
+        </is>
+      </c>
+      <c r="P2" s="0" t="inlineStr">
         <is>
           <t>images/products/JP-POST.png</t>
         </is>
@@ -766,9 +771,14 @@
       <c r="N5" s="0" t="b">
         <v>0</v>
       </c>
+      <c r="O5" s="0" t="inlineStr">
+        <is>
+          <t>images/products/JP-WOOD-TOP.png</t>
+        </is>
+      </c>
       <c r="P5" s="0" t="inlineStr">
         <is>
-          <t>images/icons/wood-top.svg</t>
+          <t>images/products/JP-WOOD-TOP.png</t>
         </is>
       </c>
       <c r="Q5" s="0" t="inlineStr">
@@ -828,7 +838,7 @@
         </is>
       </c>
       <c r="L6" s="0" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="M6" s="0" t="inlineStr">
         <is>
@@ -875,11 +885,11 @@
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t>长度300/450/500</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="L7" s="0" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="M7" s="0" t="inlineStr">
         <is>
@@ -925,7 +935,7 @@
         </is>
       </c>
       <c r="L8" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M8" s="0" t="inlineStr">
         <is>
@@ -996,9 +1006,14 @@
       <c r="N9" s="0" t="b">
         <v>0</v>
       </c>
+      <c r="O9" s="0" t="inlineStr">
+        <is>
+          <t>images/products/JP-WOOD-SHELF.png</t>
+        </is>
+      </c>
       <c r="P9" s="0" t="inlineStr">
         <is>
-          <t>images/icons/wood-shelf.svg</t>
+          <t>images/products/JP-WOOD-SHELF.png</t>
         </is>
       </c>
       <c r="Q9" s="0" t="inlineStr">
@@ -1052,7 +1067,7 @@
         </is>
       </c>
       <c r="L10" s="0" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="M10" s="0" t="inlineStr">
         <is>
@@ -1113,7 +1128,7 @@
         </is>
       </c>
       <c r="L11" s="0" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M11" s="0" t="inlineStr">
         <is>
@@ -1123,14 +1138,14 @@
       <c r="N11" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="0" t="inlineStr">
         <is>
           <t>images/products/JP-RAIL.png</t>
         </is>
       </c>
       <c r="P11" s="0" t="inlineStr">
         <is>
-          <t>images/icons/single-rail.svg</t>
+          <t>images/products/JP-RAIL.png</t>
         </is>
       </c>
       <c r="Q11" s="0" t="inlineStr">
@@ -1179,7 +1194,7 @@
         </is>
       </c>
       <c r="L12" s="0" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
@@ -1250,14 +1265,14 @@
       <c r="N13" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="0" t="inlineStr">
         <is>
           <t>images/products/JP-RAIL-DOUBLE.png</t>
         </is>
       </c>
       <c r="P13" s="0" t="inlineStr">
         <is>
-          <t>images/icons/double-rail.svg</t>
+          <t>images/products/JP-RAIL-DOUBLE.png</t>
         </is>
       </c>
       <c r="Q13" s="0" t="inlineStr">
@@ -1306,7 +1321,7 @@
         </is>
       </c>
       <c r="L14" s="0" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M14" s="0" t="inlineStr">
         <is>
@@ -1436,7 +1451,7 @@
         </is>
       </c>
       <c r="L16" s="0" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M16" s="0" t="inlineStr">
         <is>
@@ -1576,14 +1591,14 @@
       <c r="N18" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O18" s="0" t="inlineStr">
         <is>
           <t>images/products/JP-TROUSER-RACK.png</t>
         </is>
       </c>
       <c r="P18" s="0" t="inlineStr">
         <is>
-          <t>images/icons/trouser-rack.svg</t>
+          <t>images/products/JP-TROUSER-RACK.png</t>
         </is>
       </c>
       <c r="Q18" s="0" t="inlineStr">
@@ -1865,7 +1880,7 @@
         </is>
       </c>
       <c r="L23" s="0" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="M23" s="0" t="inlineStr">
         <is>
@@ -1936,7 +1951,7 @@
       </c>
       <c r="O24" s="0" t="inlineStr">
         <is>
-          <t>images/products/JP-POST-CAP.png</t>
+          <t>images/products/JP-POST-CAP-FOOT-SET.png</t>
         </is>
       </c>
       <c r="T24" s="0" t="inlineStr">
@@ -1951,6 +1966,158 @@
         <is>
           <t>每套含立柱顶盖1件、底部调节脚1件</t>
         </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>JP-POST-2000</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>立柱</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>立柱</t>
+        </is>
+      </c>
+      <c r="F25" s="0" t="inlineStr">
+        <is>
+          <t>碳钢</t>
+        </is>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>银色</t>
+        </is>
+      </c>
+      <c r="K25" s="0" t="inlineStr">
+        <is>
+          <t>2000mm</t>
+        </is>
+      </c>
+      <c r="L25" s="0" t="n">
+        <v>88</v>
+      </c>
+      <c r="M25" s="0" t="inlineStr">
+        <is>
+          <t>根</t>
+        </is>
+      </c>
+      <c r="N25" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O25" s="0" t="inlineStr">
+        <is>
+          <t>images/products/JP-POST.png</t>
+        </is>
+      </c>
+      <c r="P25" s="0" t="inlineStr">
+        <is>
+          <t>images/products/JP-POST.png</t>
+        </is>
+      </c>
+      <c r="Q25" s="0" t="inlineStr">
+        <is>
+          <t>models/glb/JP-POST.glb</t>
+        </is>
+      </c>
+      <c r="R25" s="0" t="inlineStr">
+        <is>
+          <t>models/glb/JP-POST.glb</t>
+        </is>
+      </c>
+      <c r="T25" s="0" t="inlineStr">
+        <is>
+          <t>立柱系统</t>
+        </is>
+      </c>
+      <c r="U25" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>JP-POST-2400</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>立柱</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>立柱</t>
+        </is>
+      </c>
+      <c r="F26" s="0" t="inlineStr">
+        <is>
+          <t>碳钢</t>
+        </is>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t>银色</t>
+        </is>
+      </c>
+      <c r="K26" s="0" t="inlineStr">
+        <is>
+          <t>2400mm</t>
+        </is>
+      </c>
+      <c r="L26" s="0" t="n">
+        <v>106</v>
+      </c>
+      <c r="M26" s="0" t="inlineStr">
+        <is>
+          <t>根</t>
+        </is>
+      </c>
+      <c r="N26" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O26" s="0" t="inlineStr">
+        <is>
+          <t>images/products/JP-POST.png</t>
+        </is>
+      </c>
+      <c r="P26" s="0" t="inlineStr">
+        <is>
+          <t>images/products/JP-POST.png</t>
+        </is>
+      </c>
+      <c r="Q26" s="0" t="inlineStr">
+        <is>
+          <t>models/glb/JP-POST.glb</t>
+        </is>
+      </c>
+      <c r="R26" s="0" t="inlineStr">
+        <is>
+          <t>models/glb/JP-POST.glb</t>
+        </is>
+      </c>
+      <c r="T26" s="0" t="inlineStr">
+        <is>
+          <t>立柱系统</t>
+        </is>
+      </c>
+      <c r="U26" s="0" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/products/japanese-closet/excel/products.xlsx
+++ b/products/japanese-closet/excel/products.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="12480" activeTab="1"/>
+    <workbookView windowWidth="28260" windowHeight="11720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="214">
   <si>
     <t>key</t>
   </si>
@@ -150,6 +150,9 @@
     <t>heightLocked</t>
   </si>
   <si>
+    <t>ClientOnly</t>
+  </si>
+  <si>
     <t>JP-POST</t>
   </si>
   <si>
@@ -273,7 +276,7 @@
     <t>horizontalRail</t>
   </si>
   <si>
-    <t>1m</t>
+    <t>500mm</t>
   </si>
   <si>
     <t>条</t>
@@ -291,9 +294,6 @@
     <t>cornerBracket</t>
   </si>
   <si>
-    <t>500mm</t>
-  </si>
-  <si>
     <t>个</t>
   </si>
   <si>
@@ -562,6 +562,114 @@
   </si>
   <si>
     <t>2400mm</t>
+  </si>
+  <si>
+    <t>JP-drawer-leather-storage</t>
+  </si>
+  <si>
+    <t>皮革收纳篮</t>
+  </si>
+  <si>
+    <t>drawerSingle</t>
+  </si>
+  <si>
+    <t>收纳件</t>
+  </si>
+  <si>
+    <t>images/products/JP-drawer-leather-storage.png</t>
+  </si>
+  <si>
+    <t>models/glb/JP-drawer-leather-storage.glb</t>
+  </si>
+  <si>
+    <t>收纳件系统</t>
+  </si>
+  <si>
+    <t>JP-drawer-multi-storage</t>
+  </si>
+  <si>
+    <t>装饰品收纳盒</t>
+  </si>
+  <si>
+    <t>images/products/JP-drawer-multi-storage.png</t>
+  </si>
+  <si>
+    <t>models/glb/JP-drawer-multi-storage.glb</t>
+  </si>
+  <si>
+    <t>JP-drawer-underwear-a</t>
+  </si>
+  <si>
+    <t>收纳内衣格A</t>
+  </si>
+  <si>
+    <t>images/products/JP-drawer-underwear-a.png</t>
+  </si>
+  <si>
+    <t>models/glb/JP-drawer-underwear-a.glb</t>
+  </si>
+  <si>
+    <t>JP-drawer-jewelry</t>
+  </si>
+  <si>
+    <t>多功能皮革首饰盒</t>
+  </si>
+  <si>
+    <t>images/products/JP-drawer-jewelry.png</t>
+  </si>
+  <si>
+    <t>models/glb/JP-drawer-jewelry.glb</t>
+  </si>
+  <si>
+    <t>JP-drawer-underwear-b</t>
+  </si>
+  <si>
+    <t>收纳内衣格B</t>
+  </si>
+  <si>
+    <t>images/products/JP-drawer-underwear-b.png</t>
+  </si>
+  <si>
+    <t>models/glb/JP-drawer-underwear-b.glb</t>
+  </si>
+  <si>
+    <t>JP-drawer-wire-basket</t>
+  </si>
+  <si>
+    <t>收纳网篮</t>
+  </si>
+  <si>
+    <t>images/products/JP-drawer-wire-basket.png</t>
+  </si>
+  <si>
+    <t>models/glb/JP-drawer-wire-basket.glb</t>
+  </si>
+  <si>
+    <t>JP-drawer-wire-basket-short</t>
+  </si>
+  <si>
+    <t>收纳网篮浅</t>
+  </si>
+  <si>
+    <t>images/products/JP-drawer-wire-basket-short.png</t>
+  </si>
+  <si>
+    <t>models/glb/JP-drawer-wire-basket-short.glb</t>
+  </si>
+  <si>
+    <t>JP-drawerDouble</t>
+  </si>
+  <si>
+    <t>双抽</t>
+  </si>
+  <si>
+    <t>drawerDouble</t>
+  </si>
+  <si>
+    <t>images/products/JP-drawerDouble.png</t>
+  </si>
+  <si>
+    <t>models/glb/JP-drawerDouble.glb</t>
   </si>
 </sst>
 </file>
@@ -1183,11 +1291,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1618,8 +1729,8 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="17.4411764705882" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5514705882353" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.4375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5535714285714" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1634,7 +1745,7 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1642,7 +1753,7 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1650,7 +1761,7 @@
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1658,7 +1769,7 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1666,7 +1777,7 @@
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1674,7 +1785,7 @@
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1685,37 +1796,39 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:AA35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="26.1102941176471" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.3308823529412" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.44117647058824" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.1102941176471" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6617647058824" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.44117647058824" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7794117647059" style="1" customWidth="1"/>
-    <col min="8" max="8" width="6.33088235294118" style="1" customWidth="1"/>
-    <col min="9" max="9" width="6.55147058823529" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.1071428571429" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.3303571428571" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.4375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.1071428571429" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6607142857143" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.4375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7767857142857" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6.33035714285714" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.55357142857143" style="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="1" customWidth="1"/>
-    <col min="11" max="11" width="38.8897058823529" style="1" customWidth="1"/>
+    <col min="11" max="11" width="38.8928571428571" style="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="1" customWidth="1"/>
-    <col min="13" max="13" width="4.88970588235294" style="1" customWidth="1"/>
-    <col min="14" max="14" width="7.77941176470588" style="1" customWidth="1"/>
-    <col min="15" max="15" width="46.6617647058824" style="1" customWidth="1"/>
-    <col min="16" max="16" width="30.5514705882353" style="1" customWidth="1"/>
-    <col min="17" max="18" width="33.6617647058824" style="1" customWidth="1"/>
-    <col min="19" max="19" width="20.4411764705882" style="1" customWidth="1"/>
-    <col min="20" max="20" width="11.6617647058824" style="1" customWidth="1"/>
-    <col min="21" max="21" width="9.77941176470588" style="1" customWidth="1"/>
+    <col min="13" max="13" width="4.89285714285714" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7.77678571428571" style="1" customWidth="1"/>
+    <col min="15" max="15" width="46.6607142857143" style="1" customWidth="1"/>
+    <col min="16" max="16" width="30.5535714285714" style="1" customWidth="1"/>
+    <col min="17" max="17" width="45.9732142857143" style="1" customWidth="1"/>
+    <col min="18" max="18" width="33.6607142857143" style="1" customWidth="1"/>
+    <col min="19" max="19" width="20.4375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.6607142857143" style="1" customWidth="1"/>
+    <col min="21" max="21" width="9.77678571428571" style="1" customWidth="1"/>
     <col min="22" max="22" width="11" style="1" customWidth="1"/>
-    <col min="23" max="23" width="11.4411764705882" style="1" customWidth="1"/>
-    <col min="24" max="24" width="8.44117647058824" style="1" customWidth="1"/>
+    <col min="23" max="23" width="11.4375" style="1" customWidth="1"/>
+    <col min="24" max="24" width="8.4375" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.2589285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1794,178 +1907,190 @@
       <c r="Z1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:26">
+      <c r="AA1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" t="s">
         <v>42</v>
       </c>
-      <c r="E2" t="s">
-        <v>41</v>
-      </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L2">
         <v>85</v>
       </c>
       <c r="M2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U2">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:26">
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L3">
         <v>8.5</v>
       </c>
       <c r="M3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U3">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:26">
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L4">
         <v>8.5</v>
       </c>
       <c r="M4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
       </c>
       <c r="O4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="T4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U4">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:26">
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="T5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U5">
         <v>20</v>
@@ -1976,97 +2101,104 @@
       <c r="Z5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:26">
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L6">
         <v>28</v>
       </c>
       <c r="M6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
       </c>
       <c r="O6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U6">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:26">
+      <c r="AA6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>75</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>500mm</t>
-        </is>
+        <v>76</v>
+      </c>
+      <c r="K7" t="s">
+        <v>82</v>
       </c>
       <c r="L7">
         <v>28</v>
       </c>
       <c r="M7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U7">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:26">
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="L8">
         <v>3</v>
@@ -2081,13 +2213,16 @@
         <v>89</v>
       </c>
       <c r="T8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U8">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:26">
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9" t="s">
         <v>90</v>
       </c>
@@ -2098,22 +2233,22 @@
         <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
@@ -2136,8 +2271,11 @@
       <c r="U9">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:26">
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10" t="s">
         <v>96</v>
       </c>
@@ -2151,16 +2289,16 @@
         <v>99</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L10">
         <v>28</v>
       </c>
       <c r="M10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -2174,8 +2312,11 @@
       <c r="U10">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" spans="1:26">
+      <c r="AA10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11" t="s">
         <v>101</v>
       </c>
@@ -2186,13 +2327,13 @@
         <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K11" t="s">
         <v>104</v>
@@ -2201,7 +2342,7 @@
         <v>16</v>
       </c>
       <c r="M11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -2224,8 +2365,11 @@
       <c r="U11">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:26">
+      <c r="AA11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27">
       <c r="A12" t="s">
         <v>108</v>
       </c>
@@ -2239,13 +2383,13 @@
         <v>111</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L12">
         <v>15</v>
       </c>
       <c r="M12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -2259,8 +2403,11 @@
       <c r="U12">
         <v>40</v>
       </c>
-    </row>
-    <row r="13" spans="1:26">
+      <c r="AA12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27">
       <c r="A13" t="s">
         <v>113</v>
       </c>
@@ -2271,13 +2418,13 @@
         <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K13" t="s">
         <v>104</v>
@@ -2286,7 +2433,7 @@
         <v>30</v>
       </c>
       <c r="M13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -2309,8 +2456,11 @@
       <c r="U13">
         <v>40</v>
       </c>
-    </row>
-    <row r="14" spans="1:26">
+      <c r="AA13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27">
       <c r="A14" t="s">
         <v>118</v>
       </c>
@@ -2324,13 +2474,13 @@
         <v>111</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L14">
         <v>20</v>
       </c>
       <c r="M14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -2344,8 +2494,11 @@
       <c r="U14">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" spans="1:26">
+      <c r="AA14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27">
       <c r="A15" t="s">
         <v>122</v>
       </c>
@@ -2356,13 +2509,13 @@
         <v>124</v>
       </c>
       <c r="E15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K15" t="s">
         <v>125</v>
@@ -2397,8 +2550,11 @@
       <c r="X15" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26">
+      <c r="AA15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27">
       <c r="A16" t="s">
         <v>130</v>
       </c>
@@ -2412,13 +2568,13 @@
         <v>133</v>
       </c>
       <c r="F16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L16">
         <v>15</v>
       </c>
       <c r="M16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -2432,8 +2588,11 @@
       <c r="U16">
         <v>50</v>
       </c>
-    </row>
-    <row r="17" spans="1:24">
+      <c r="AA16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27">
       <c r="A17" t="s">
         <v>135</v>
       </c>
@@ -2444,10 +2603,10 @@
         <v>137</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K17" t="s">
         <v>138</v>
@@ -2485,8 +2644,11 @@
       <c r="X17" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:24">
+      <c r="AA17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27">
       <c r="A18" t="s">
         <v>142</v>
       </c>
@@ -2497,10 +2659,10 @@
         <v>144</v>
       </c>
       <c r="E18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L18">
         <v>270</v>
@@ -2529,8 +2691,11 @@
       <c r="U18">
         <v>50</v>
       </c>
-    </row>
-    <row r="19" spans="1:24">
+      <c r="AA18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27">
       <c r="A19" t="s">
         <v>147</v>
       </c>
@@ -2544,16 +2709,16 @@
         <v>150</v>
       </c>
       <c r="F19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L19">
         <v>25</v>
       </c>
       <c r="M19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -2567,8 +2732,11 @@
       <c r="U19">
         <v>50</v>
       </c>
-    </row>
-    <row r="20" spans="1:24">
+      <c r="AA19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20" t="s">
         <v>152</v>
       </c>
@@ -2582,7 +2750,7 @@
         <v>155</v>
       </c>
       <c r="F20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K20" t="s">
         <v>156</v>
@@ -2591,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -2608,8 +2776,11 @@
       <c r="X20" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:24">
+      <c r="AA20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27">
       <c r="A21" t="s">
         <v>157</v>
       </c>
@@ -2623,7 +2794,7 @@
         <v>155</v>
       </c>
       <c r="F21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K21" t="s">
         <v>159</v>
@@ -2632,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -2649,8 +2820,11 @@
       <c r="X21" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:24">
+      <c r="AA21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27">
       <c r="A22" t="s">
         <v>160</v>
       </c>
@@ -2664,7 +2838,7 @@
         <v>155</v>
       </c>
       <c r="F22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K22" t="s">
         <v>163</v>
@@ -2673,7 +2847,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -2690,8 +2864,11 @@
       <c r="X22" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:24">
+      <c r="AA22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27">
       <c r="A23" t="s">
         <v>164</v>
       </c>
@@ -2728,8 +2905,11 @@
       <c r="X23" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:24">
+      <c r="AA23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27">
       <c r="A24" t="s">
         <v>168</v>
       </c>
@@ -2740,13 +2920,13 @@
         <v>170</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L24">
         <v>8.5</v>
@@ -2761,7 +2941,7 @@
         <v>172</v>
       </c>
       <c r="T24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -2769,25 +2949,28 @@
       <c r="V24" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="25" spans="1:24">
+      <c r="AA24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27">
       <c r="A25" t="s">
         <v>174</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" t="s">
         <v>42</v>
       </c>
-      <c r="E25" t="s">
-        <v>41</v>
-      </c>
       <c r="F25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K25" t="s">
         <v>175</v>
@@ -2796,48 +2979,51 @@
         <v>88</v>
       </c>
       <c r="M25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
       </c>
       <c r="O25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U25">
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="1:24">
+      <c r="AA25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27">
       <c r="A26" t="s">
         <v>176</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D26" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" t="s">
         <v>42</v>
       </c>
-      <c r="E26" t="s">
-        <v>41</v>
-      </c>
       <c r="F26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K26" t="s">
         <v>177</v>
@@ -2846,29 +3032,456 @@
         <v>106</v>
       </c>
       <c r="M26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
       </c>
       <c r="O26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U26">
         <v>10</v>
       </c>
+      <c r="AA26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27">
+      <c r="A27" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" t="s">
+        <v>45</v>
+      </c>
+      <c r="K27" t="s">
+        <v>138</v>
+      </c>
+      <c r="L27" s="1">
+        <v>750</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N27" t="b">
+        <v>1</v>
+      </c>
+      <c r="O27" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>183</v>
+      </c>
+      <c r="R27" t="s">
+        <v>183</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="U27" s="1">
+        <v>60</v>
+      </c>
+      <c r="W27" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27">
+      <c r="A28" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" t="s">
+        <v>45</v>
+      </c>
+      <c r="K28" t="s">
+        <v>138</v>
+      </c>
+      <c r="L28" s="1">
+        <v>650</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N28" t="b">
+        <v>1</v>
+      </c>
+      <c r="O28" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>188</v>
+      </c>
+      <c r="R28" t="s">
+        <v>188</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="U28" s="1">
+        <v>60</v>
+      </c>
+      <c r="W28" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27">
+      <c r="A29" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" t="s">
+        <v>45</v>
+      </c>
+      <c r="K29" t="s">
+        <v>138</v>
+      </c>
+      <c r="L29" s="1">
+        <v>850</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O29" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>192</v>
+      </c>
+      <c r="R29" t="s">
+        <v>192</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="U29" s="1">
+        <v>60</v>
+      </c>
+      <c r="W29" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27">
+      <c r="A30" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F30" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" t="s">
+        <v>45</v>
+      </c>
+      <c r="K30" t="s">
+        <v>138</v>
+      </c>
+      <c r="L30" s="1">
+        <v>880</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N30" t="b">
+        <v>1</v>
+      </c>
+      <c r="O30" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>196</v>
+      </c>
+      <c r="R30" t="s">
+        <v>196</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="U30" s="1">
+        <v>60</v>
+      </c>
+      <c r="W30" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27">
+      <c r="A31" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F31" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" t="s">
+        <v>45</v>
+      </c>
+      <c r="K31" t="s">
+        <v>138</v>
+      </c>
+      <c r="L31" s="1">
+        <v>880</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O31" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>200</v>
+      </c>
+      <c r="R31" t="s">
+        <v>200</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="U31" s="1">
+        <v>60</v>
+      </c>
+      <c r="W31" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27">
+      <c r="A32" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F32" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" t="s">
+        <v>45</v>
+      </c>
+      <c r="K32" t="s">
+        <v>138</v>
+      </c>
+      <c r="L32" s="1">
+        <v>500</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N32" t="b">
+        <v>1</v>
+      </c>
+      <c r="O32" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>204</v>
+      </c>
+      <c r="R32" t="s">
+        <v>204</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="U32" s="1">
+        <v>60</v>
+      </c>
+      <c r="W32" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27">
+      <c r="A33" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F33" t="s">
+        <v>44</v>
+      </c>
+      <c r="G33" t="s">
+        <v>45</v>
+      </c>
+      <c r="K33" t="s">
+        <v>138</v>
+      </c>
+      <c r="L33" s="1">
+        <v>550</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N33" t="b">
+        <v>1</v>
+      </c>
+      <c r="O33" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>208</v>
+      </c>
+      <c r="R33" t="s">
+        <v>208</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="U33" s="1">
+        <v>60</v>
+      </c>
+      <c r="W33" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27">
+      <c r="A34" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F34" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" t="s">
+        <v>45</v>
+      </c>
+      <c r="K34" t="s">
+        <v>138</v>
+      </c>
+      <c r="L34" s="1">
+        <v>160</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
+      </c>
+      <c r="O34" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>213</v>
+      </c>
+      <c r="R34" t="s">
+        <v>213</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="U34" s="1">
+        <v>60</v>
+      </c>
+      <c r="W34" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27">
+      <c r="W35"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/products/japanese-closet/excel/products.xlsx
+++ b/products/japanese-closet/excel/products.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="11720" activeTab="1"/>
+    <workbookView windowWidth="28260" windowHeight="12820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="229">
   <si>
     <t>key</t>
   </si>
@@ -153,6 +153,9 @@
     <t>ClientOnly</t>
   </si>
   <si>
+    <t>JapaneseClientPrice</t>
+  </si>
+  <si>
     <t>JP-POST</t>
   </si>
   <si>
@@ -670,6 +673,48 @@
   </si>
   <si>
     <t>models/glb/JP-drawerDouble.glb</t>
+  </si>
+  <si>
+    <t>JP-CLOTH-BOARD</t>
+  </si>
+  <si>
+    <t>烫衣板</t>
+  </si>
+  <si>
+    <t>clothBoard</t>
+  </si>
+  <si>
+    <t>配件</t>
+  </si>
+  <si>
+    <t>fault</t>
+  </si>
+  <si>
+    <t>images/products/JP-CLOTH-BOARD.png</t>
+  </si>
+  <si>
+    <t>models/glb/JP-CLOTH-BOARD.glb</t>
+  </si>
+  <si>
+    <t>配件系统</t>
+  </si>
+  <si>
+    <t>JP-MIRROR</t>
+  </si>
+  <si>
+    <t>镜子</t>
+  </si>
+  <si>
+    <t>mirror</t>
+  </si>
+  <si>
+    <t>面</t>
+  </si>
+  <si>
+    <t>images/products/JP-MIRROR.png</t>
+  </si>
+  <si>
+    <t>models/glb/JP-MIRROR.glb</t>
   </si>
 </sst>
 </file>
@@ -1798,7 +1843,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA35"/>
+  <dimension ref="A1:AB36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="26.1071428571429" style="1" customWidth="1"/>
@@ -1826,9 +1871,10 @@
     <col min="23" max="23" width="11.4375" style="1" customWidth="1"/>
     <col min="24" max="24" width="8.4375" style="1" customWidth="1"/>
     <col min="27" max="27" width="10.2589285714286" customWidth="1"/>
+    <col min="28" max="28" width="18.1517857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:28">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1910,52 +1956,55 @@
       <c r="AA1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:27">
+      <c r="AB1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" t="s">
         <v>43</v>
       </c>
-      <c r="E2" t="s">
-        <v>42</v>
-      </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L2">
         <v>85</v>
       </c>
       <c r="M2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U2">
         <v>10</v>
@@ -1964,39 +2013,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:28">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L3">
         <v>8.5</v>
       </c>
       <c r="M3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U3">
         <v>10</v>
@@ -2005,39 +2054,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:28">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L4">
         <v>8.5</v>
       </c>
       <c r="M4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
       </c>
       <c r="O4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -2046,51 +2095,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:28">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U5">
         <v>20</v>
@@ -2104,40 +2153,43 @@
       <c r="AA5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:27">
+      <c r="AB5">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L6">
         <v>28</v>
       </c>
       <c r="M6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
       </c>
       <c r="O6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U6">
         <v>20</v>
@@ -2146,36 +2198,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:28">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L7">
         <v>28</v>
       </c>
       <c r="M7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U7">
         <v>20</v>
@@ -2184,36 +2236,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:28">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L8">
         <v>3</v>
       </c>
       <c r="M8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
       </c>
       <c r="O8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U8">
         <v>20</v>
@@ -2222,51 +2274,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:28">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="T9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="U9">
         <v>30</v>
@@ -2274,40 +2326,43 @@
       <c r="AA9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:27">
+      <c r="AB9">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L10">
         <v>28</v>
       </c>
       <c r="M10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
       </c>
       <c r="O10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="U10">
         <v>30</v>
@@ -2316,51 +2371,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:28">
       <c r="A11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L11">
         <v>16</v>
       </c>
       <c r="M11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
       </c>
       <c r="O11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U11">
         <v>40</v>
@@ -2368,37 +2423,40 @@
       <c r="AA11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:27">
+      <c r="AB11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L12">
         <v>15</v>
       </c>
       <c r="M12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
       </c>
       <c r="O12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="T12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U12">
         <v>40</v>
@@ -2407,51 +2465,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:28">
       <c r="A13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L13">
         <v>30</v>
       </c>
       <c r="M13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
       </c>
       <c r="O13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="R13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U13">
         <v>40</v>
@@ -2459,37 +2517,40 @@
       <c r="AA13" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27">
+      <c r="AB13">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28">
       <c r="A14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L14">
         <v>20</v>
       </c>
       <c r="M14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
       </c>
       <c r="O14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="T14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U14">
         <v>40</v>
@@ -2498,54 +2559,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:28">
       <c r="A15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="U15">
         <v>50</v>
       </c>
       <c r="W15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="X15" t="b">
         <v>0</v>
@@ -2553,37 +2614,40 @@
       <c r="AA15" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27">
+      <c r="AB15">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28">
       <c r="A16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L16">
         <v>15</v>
       </c>
       <c r="M16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="T16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="U16">
         <v>50</v>
@@ -2592,54 +2656,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:28">
       <c r="A17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L17">
         <v>300</v>
       </c>
       <c r="M17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
       </c>
       <c r="O17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="R17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="T17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="U17">
         <v>50</v>
       </c>
       <c r="W17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="X17" t="b">
         <v>0</v>
@@ -2647,46 +2711,49 @@
       <c r="AA17" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:27">
+      <c r="AB17">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28">
       <c r="A18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L18">
         <v>270</v>
       </c>
       <c r="M18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
       </c>
       <c r="O18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="T18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="U18">
         <v>50</v>
@@ -2694,40 +2761,43 @@
       <c r="AA18" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:27">
+      <c r="AB18">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28">
       <c r="A19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L19">
         <v>25</v>
       </c>
       <c r="M19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
       </c>
       <c r="O19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="T19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="U19">
         <v>50</v>
@@ -2736,42 +2806,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:28">
       <c r="A20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E20" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K20" t="s">
+        <v>157</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="s">
+        <v>61</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="s">
         <v>156</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20" t="s">
-        <v>60</v>
-      </c>
-      <c r="N20" t="b">
-        <v>1</v>
-      </c>
-      <c r="T20" t="s">
-        <v>155</v>
       </c>
       <c r="U20">
         <v>95</v>
       </c>
       <c r="W20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="X20" t="b">
         <v>0</v>
@@ -2780,42 +2850,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:28">
       <c r="A21" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D21" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
       </c>
       <c r="T21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U21">
         <v>95</v>
       </c>
       <c r="W21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="X21" t="b">
         <v>0</v>
@@ -2824,42 +2894,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:28">
       <c r="A22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K22" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
       </c>
       <c r="T22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U22">
         <v>95</v>
       </c>
       <c r="W22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="X22" t="b">
         <v>0</v>
@@ -2868,39 +2938,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:28">
       <c r="A23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L23">
         <v>0.25</v>
       </c>
       <c r="M23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
       </c>
       <c r="T23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U23">
         <v>95</v>
       </c>
       <c r="W23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="X23" t="b">
         <v>0</v>
@@ -2909,95 +2979,95 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:28">
       <c r="A24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D24" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L24">
         <v>8.5</v>
       </c>
       <c r="M24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
       </c>
       <c r="O24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U24">
         <v>10</v>
       </c>
       <c r="V24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:28">
       <c r="A25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
         <v>43</v>
       </c>
-      <c r="E25" t="s">
-        <v>42</v>
-      </c>
       <c r="F25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K25" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L25">
         <v>88</v>
       </c>
       <c r="M25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
       </c>
       <c r="O25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U25">
         <v>10</v>
@@ -3006,51 +3076,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:28">
       <c r="A26" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
         <v>43</v>
       </c>
-      <c r="E26" t="s">
-        <v>42</v>
-      </c>
       <c r="F26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K26" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L26">
         <v>106</v>
       </c>
       <c r="M26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
       </c>
       <c r="O26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U26">
         <v>10</v>
@@ -3059,429 +3129,553 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:28">
       <c r="A27" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L27" s="1">
         <v>750</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
       </c>
       <c r="O27" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q27" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="R27" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U27" s="1">
         <v>60</v>
       </c>
       <c r="W27" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AA27" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:27">
+      <c r="AB27">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28">
       <c r="A28" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K28" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L28" s="1">
         <v>650</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
       </c>
       <c r="O28" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="R28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U28" s="1">
         <v>60</v>
       </c>
       <c r="W28" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AA28" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:27">
+      <c r="AB28">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28">
       <c r="A29" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L29" s="1">
         <v>850</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
       </c>
       <c r="O29" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q29" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R29" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U29" s="1">
         <v>60</v>
       </c>
       <c r="W29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AA29" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:27">
+      <c r="AB29">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28">
       <c r="A30" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L30" s="1">
         <v>880</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
       </c>
       <c r="O30" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q30" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="R30" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U30" s="1">
         <v>60</v>
       </c>
       <c r="W30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AA30" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:27">
+      <c r="AB30">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28">
       <c r="A31" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K31" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L31" s="1">
         <v>880</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
       </c>
       <c r="O31" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q31" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="R31" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U31" s="1">
         <v>60</v>
       </c>
       <c r="W31" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AA31" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:27">
+      <c r="AB31">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28">
       <c r="A32" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K32" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L32" s="1">
         <v>500</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
       </c>
       <c r="O32" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q32" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="R32" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U32" s="1">
         <v>60</v>
       </c>
       <c r="W32" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AA32" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:27">
+      <c r="AB32">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28">
       <c r="A33" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L33" s="1">
         <v>550</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q33" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="R33" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U33" s="1">
         <v>60</v>
       </c>
       <c r="W33" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AA33" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:27">
+      <c r="AB33">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28">
       <c r="A34" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L34" s="1">
         <v>160</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
       </c>
       <c r="O34" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q34" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R34" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U34" s="1">
         <v>60</v>
       </c>
       <c r="W34" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27">
+        <v>130</v>
+      </c>
+      <c r="AA34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28">
+      <c r="A35" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="L35" s="1">
+        <v>250</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
+      </c>
+      <c r="O35" t="s">
+        <v>220</v>
+      </c>
+      <c r="P35"/>
+      <c r="Q35" t="s">
+        <v>221</v>
+      </c>
+      <c r="R35" t="s">
+        <v>221</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="U35" s="1">
+        <v>70</v>
+      </c>
       <c r="W35"/>
+      <c r="X35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28">
+      <c r="A36" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="L36" s="1">
+        <v>75</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
+      </c>
+      <c r="O36" t="s">
+        <v>227</v>
+      </c>
+      <c r="P36"/>
+      <c r="Q36" t="s">
+        <v>228</v>
+      </c>
+      <c r="R36" t="s">
+        <v>228</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="U36" s="1">
+        <v>70</v>
+      </c>
+      <c r="X36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>150</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
